--- a/AI_AuditLog_DuongTruongSon.xlsx
+++ b/AI_AuditLog_DuongTruongSon.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Semeter 5\SWP391\ai-audit-log-dson3009\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09AEAB59-7305-4125-B727-E7B33AEB6840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C1AEC89-87A5-4E8E-806E-2244D4620D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1080" windowWidth="28800" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
     <sheet name="Week 2" sheetId="2" r:id="rId2"/>
     <sheet name="Week 3" sheetId="3" r:id="rId3"/>
     <sheet name="Week 4" sheetId="4" r:id="rId4"/>
+    <sheet name="Week 5" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="69">
   <si>
     <t>STT</t>
   </si>
@@ -209,6 +210,63 @@
 • Contextualization: Ứng dụng quản lý lịch hẹn cao cấp như Aura Spa không cho phép bất kỳ sai số nào về mặt thời gian vận hành vì nó sẽ phá vỡ toàn bộ cấu trúc thuật toán phân ca ở các tuần sau.
 • Creative Synthesis: Tôi đã loại bỏ hoàn toàn giải pháp lạc hậu của AI. Tôi xây dựng lớp `InputValidator` dựa trên nền tảng Modern Java Time API (Java 8+). Đối với số điện thoại, tôi nâng cấp Regex thành: `^(03|05|07|08|09)\d{8}$` để bao quát chính xác các đầu số nhà mạng hiện đại tại Việt Nam. Đối với ngày giờ, tôi sử dụng lớp `DateTimeFormatter` cấu hình nghiêm ngặt với thuộc tính `withResolverStyle(ResolverStyle.STRICT)`. Đoạn code kiểm tra được viết lại bằng cách gọi `LocalDateTime.parse(input, formatter)`. Khi chế độ STRICT được kích hoạt, bất kỳ ngày nào không tồn tại trên lịch (như 29/02 của năm không nhuận) hoặc giờ giấc vượt quá 23:59 sẽ lập tức bị ném vào khối lệnh `catch (DateTimeParseException)` và ép người dùng phải nhập lại.
 • Decision Ownership: Quyết định áp dụng Modern Java Time API với chế độ kiểm tra nghiêm ngặt giúp dự án xây dựng được một 'lá chắn' nhập liệu vững chắc ngay tại tầng giao diện UI. Hệ thống được đảm bảo 100% sạch bóng dữ liệu rác, tạo tiền đề cho các thao tác tính toán dòng thời gian chính xác tuyệt đối.</t>
+  </si>
+  <si>
+    <t>Algorithms / Optimization</t>
+  </si>
+  <si>
+    <t>Xây dựng cấu trúc thuật toán tổng hợp báo cáo tài chính doanh thu chi nhánh cuối tháng và trích xuất tỷ lệ trích thưởng hoa hồng (Commission) tự động cho đội ngũ kỹ thuật viên dựa trên hiệu suất làm việc thực tế.</t>
+  </si>
+  <si>
+    <t>Hãy viết một thuật toán bằng Java để giúp quản lý Aura Spa tính toán tổng doanh thu thực thu của một chi nhánh trong tháng và tự động trích xuất 5% tổng giá trị dịch vụ làm tiền thưởng hoa hồng cho từng Kỹ thuật viên (Therapist) dựa trên những ca làm việc họ đã hoàn thành thành công.</t>
+  </si>
+  <si>
+    <t>AI hướng dẫn thuật toán bằng cách duyệt qua danh sách hóa đơn toàn hệ thống, kiểm tra nếu hóa đơn thuộc chi nhánh mục tiêu và có trạng thái `STATUS_PAID` thì cộng dồn giá trị dịch vụ vào một biến tổng doanh thu. Để tính hoa hồng cho nhân viên, AI đề xuất duyệt qua danh sách lịch hẹn thành công của từng người, lấy số lượng cuộc hẹn nhân với đơn giá niêm yết của dịch vụ đó trong danh mục hệ thống rồi nhân tiếp với hệ số 0.05.</t>
+  </si>
+  <si>
+    <t>• Critical Thinking: Thuật toán tính hoa hồng của AI mắc phải một lỗi nghiêm trọng về tư duy kinh tế tài chính thực tế. Việc tính toán hoa hồng dựa trên 'đơn giá niêm yết' của dịch vụ là hoàn toàn sai lầm và gây tổn hại trực tiếp đến quỹ vận hành của spa. Trong thực tế, khách hàng thường xuyên áp dụng mã Voucher giảm giá, hoặc họ sử dụng các buổi lẻ nằm trong một gói liệu trình mua sỉ dài hạn (vốn đã được chiết khấu giảm giá lên đến 30% so với giá mua lẻ). Nếu hệ thống trích 5% dựa trên giá niêm yết ban đầu, số tiền hoa hồng trả cho nhân viên sẽ bị phóng đại lên rất nhiều so với số tiền thực tế mà spa thu được từ khách hàng, dẫn đến nguy cơ thâm hụt ngân sách nghiêm trọng.
+• Contextualization: 🎯 Yêu cầu mở rộng cho Week 4 đặt ra bài toán tối ưu hóa tài chính doanh nghiệp: Mọi khoản trích thưởng phải dựa trên cơ sở Dòng tiền thực thu (Net Revenue) chứ không dựa trên Tổng doanh thu danh nghĩa (Gross Revenue).
+• Creative Synthesis: Để sửa đổi lỗ hổng tài chính này, tôi đã tiến hành thiết kế lại cấu trúc thuật toán phân bổ dòng tiền. Trong thực thể `InvoiceItem`, tôi bổ sung một trường dữ liệu động là `actualPaidAmount` (số tiền thực trả sau khi đã trừ tỷ lệ phân bổ của Voucher). Đối với các gói liệu trình dài hạn, tôi áp dụng công thức tính giá trị phân bổ cho từng buổi lẻ: `actualAmountPerSession = totalAmountPaidForPackage / totalSessions`. Khi thuật toán tính hoa hồng chạy, hệ thống của tôi sẽ truy cập vào từng thực thể `TreatmentSessionLog` hoặc `Appointment` đã hoàn thành, bóc tách chính xác giá trị thực thu của buổi đó (`actualAmountPerSession`), rồi mới thực hiện nhân với hệ số 5%. Đồng thời, tôi sử dụng cấu trúc `StringBuilder` kết hợp với định dạng chuỗi `String.format` để xây dựng một module xuất báo cáo tài chính trực quan dưới dạng bảng Console sắc nét, bao gồm các cột: Tên nhân viên, Số ca phục vụ, Doanh thu mang lại, và Tiền hoa hồng thực nhận.
+• Decision Ownership: Tôi chốt sử dụng thuật toán tính hoa hồng dựa trên dòng tiền phân bổ thực thu làm tiêu chuẩn cho module kế toán của dự án. Giải pháp này giúp bảo vệ biên lợi nhuận an toàn cho chuỗi Aura Spa, chứng minh được tư duy quản lý vận hành thực tế vượt trội của nhóm trước hội đồng chấm đồ án và nâng cao điểm số ở phần tính năng nâng cao.</t>
+  </si>
+  <si>
+    <t>Algorithms / Research stage</t>
+  </si>
+  <si>
+    <t>Tối ưu hóa vòng đời ứng dụng (Application Lifecycle), thực hiện refactor mã nguồn để xử lý triệt để hiện tượng rò rỉ dữ liệu (Data Loss) và hỏng tệp tin cấu trúc JSON khi người dùng tắt ứng dụng console đột ngột.</t>
+  </si>
+  <si>
+    <t>Ứng dụng Java Console của tôi lưu dữ liệu vào file JSON khi chọn chức năng 'Thoát' từ menu. Tuy nhiên, nếu người dùng vô tình tắt cửa sổ dòng lệnh bằng nút X hoặc hệ thống bị ngắt đột ngột, toàn bộ dữ liệu tạm trong bộ nhớ của phiên làm việc đó sẽ bị biến mất. AI hãy đề xuất giải pháp xử lý triệt để vấn đề rò rỉ dữ liệu này.</t>
+  </si>
+  <si>
+    <t>AI đề xuất một giải pháp mang tính kỹ thuật nâng cao: Sử dụng cơ chế Java Shutdown Hook bằng lệnh `Runtime.getRuntime().addShutdownHook(new Thread(() -&gt; saveAllData()))`. AI giải thích rằng cơ chế này sẽ đăng ký một luồng chạy ngầm với JVM; khi JVM nhận tín hiệu chuẩn bị đóng chương trình (kể cả khi tắt bảng console), luồng ngầm này sẽ được kích hoạt để ép hệ thống thực hiện hàm lưu dữ liệu xuống file JSON trước khi chết hoàn toàn.</t>
+  </si>
+  <si>
+    <t>• Critical Thinking: Đề xuất sử dụng Shutdown Hook của AI chứa đựng rủi ro kỹ thuật cực kỳ lớn liên quan đến hiện tượng tương tranh và xung đột tài nguyên tệp tin (Race Condition). Ứng dụng Java Console của chúng ta là một ứng dụng đơn luồng (Single-threaded App) truy cập file tuần tự. Nếu người dùng chọn thoát ứng dụng một cách chính thống thông qua menu (đã có sẵn hàm gọi lưu file), hệ thống đang thực hiện ghi dữ liệu xuống đĩa. Đúng lúc đó, JVM đóng lại và kích hoạt tiếp Shutdown Hook chạy song song. Hai luồng dữ liệu cùng lúc ghi đè (write override) vào một tệp tin JSON duy nhất sẽ làm cho tệp tin bị tranh chấp, dẫn đến hiện tượng file dữ liệu bị xóa sạch nội dung và trả về kích thước 0-byte (Corrupted Data File). Hệ thống sẽ hoàn toàn sụp đổ ở lần khởi động tiếp theo.
+• Contextualization: Môi trường lưu trữ dạng file thô đòi hỏi sự an toàn và đơn giản tuyệt đối trong luồng ghi dữ liệu, tránh xa các giải pháp đa luồng phức tạp không thể kiểm soát kiểm thử.
+• Creative Synthesis: Tôi đã chủ động loại bỏ hoàn toàn giải pháp Shutdown Hook đầy rủi ro của AI. Thay vào đó, tôi triển khai một chiến lược lưu trữ có tên là 'Cơ chế ghi tức thời bảo toàn' (Write-Through Persistence Strategy). Tôi phân rã và nhúng trực tiếp hàm `DatabaseManager.saveChanges()` vào cuối tất cả các phương thức nghiệp vụ có khả năng làm thay đổi trạng thái dữ liệu ở tầng Service (ví dụ: ngay sau khi một lịch đặt được tạo thành công, ngay sau khi một hóa đơn được nhấn thanh toán). Dữ liệu trong bộ nhớ luôn được đồng bộ ngay lập tức xuống đĩa cứng. Bên cạnh đó, ở hàm Main của chương trình, tôi áp dụng cấu trúc quản lý tài nguyên tự động `try-with-resources` cho toàn bộ các luồng đọc dữ liệu đầu vào `Scanner`, đảm bảo các luồng này luôn được đóng một cách an toàn và giải phóng bộ nhớ đệm sạch sẽ.
+• Decision Ownership: Việc lựa chọn cơ chế Write-Through tuy làm tăng tần suất I/O file nhẹ nhưng đổi lại sự an toàn tuyệt đối cho cơ sở dữ liệu giả lập của đồ án Aura Spa. Qua các bài kiểm thử phá hủy (như tắt ngang app khi đang chạy), file dữ liệu vẫn toàn vẹn 100%, triệt tiêu hoàn toàn rủi ro mất mát thông tin.</t>
+  </si>
+  <si>
+    <t>Pattern Recognition / Software Engineering</t>
+  </si>
+  <si>
+    <t>Thực hiện tái cấu trúc mã nguồn toàn diện (Global Refactoring) nhằm loại bỏ sự trùng lặp mã nguồn (Code Duplication) ở các lớp quản lý giao diện dòng lệnh, áp dụng mô hình thiết kế hướng đối tượng nâng cao.</t>
+  </si>
+  <si>
+    <t>Tôi đã viết xong 4 lớp Menu xử lý giao diện dòng lệnh bao gồm: `AdminMenu`, `ManagerMenu`, `TherapistMenu`, và `CustomerMenu`. Tôi nhận thấy cấu trúc của 4 lớp này rất giống nhau: đều có một vòng lặp `while(true)`, hiển thị danh sách các lựa chọn, dùng Scanner đọc số nguyên, dùng `switch-case` để gọi hàm nghiệp vụ và dùng khối lệnh `try-catch` để bắt lỗi nhập sai định dạng. Làm thế nào để refactor mã nguồn tuân thủ nguyên lý DRY (Don't Repeat Yourself)?</t>
+  </si>
+  <si>
+    <t>AI đề xuất áp dụng mẫu thiết kế Template Method Pattern. AI hướng dẫn tạo một lớp cha trừu tượng tên là `BaseMenu`. Trong lớp này, định nghĩa một phương thức mẫu cụ thể mang tên `public void display()`. Phương thức này sẽ chứa toàn bộ khung vòng lặp `while` và luồng xử lý chung. AI để lại hai phương thức trừu tượng là `protected abstract void printMenuOptions()` và `protected abstract void handleUserChoice(int choice)` để các lớp menu con tự override theo nhu cầu giao diện riêng biệt.</t>
+  </si>
+  <si>
+    <t>• Critical Thinking: Kiến trúc Template Method mà AI cung cấp là một giải pháp rất chuẩn xác về mặt lý thuyết OOP. Tuy nhiên, khung code skeleton mà AI sinh ra lại mắc một lỗi bảo mật nhập liệu cơ bản ở tầng Console: AI thực hiện đọc số nguyên trực tiếp bằng lệnh `scanner.nextInt()`. Lệnh này không tự động xóa bỏ ký tự xuống dòng (`\n`) trong bộ đệm của bàn phím. Khi người dùng nhập một chuỗi ký tự chữ thay vì số, chương trình sẽ lập tức rơi vào một vòng lặp vô tận (Infinite Loop) của thông báo lỗi, làm treo toàn bộ ứng dụng console và ép người dùng phải kill tiến trình.
+• Contextualization: 🎯 Yêu cầu mở rộng cho Week 4 đòi hỏi mã nguồn sau khi refactor không chỉ sạch đẹp về mặt cấu trúc kiến trúc mà còn phải đạt được độ bền bỉ cao trước các hành vi phá hoại vô tình hoặc cố ý của người dùng cuối khi nhập liệu sai.
+• Creative Synthesis: Tôi đã giữ nguyên bộ khung Template Method cực đẹp của AI nhưng tiến hành cải tiến sâu ở tầng xử lý input. Trong lớp cha trừu tượng `BaseMenu`, tôi tự xây dựng một phương thức tiện ích bảo mật tên là `protected int readValidIntegerInput(String prompt, int min, int max)`. Bên trong phương thức này, tôi sử dụng lệnh `scanner.nextLine()` để đọc toàn bộ dòng dưới dạng chuỗi thô (loại bỏ hoàn toàn lỗi kẹt ký tự `\n`), sau đó đưa chuỗi vào phương thức `Integer.parseInt(input.trim())` bọc trong một khối lệnh `try-catch (NumberFormatException)`. Nếu người dùng nhập sai, hệ thống sẽ hiển thị cảnh báo đỏ và cho phép nhập lại tối đa 3 lần (`MAX_RETRIES = 3`). Nếu vượt quá, hệ thống tự động quay lại menu gốc thay vì treo máy.
+• Decision Ownership: Tôi đã tiến hành áp dụng lớp `BaseMenu` cải tiến này để refactor lại toàn bộ hệ thống giao diện dòng lệnh của Aura Spa. Kết quả vô cùng ấn tượng: tổng số dòng tổng thể của tầng UI giảm từ hơn 450 dòng xuống chỉ còn chưa đầy 180 dòng. Mã nguồn trở nên cực kỳ tinh gọn, phô diễn kỹ năng vận dụng Design Pattern xuất sắc và khả năng xử lý ngoại lệ kiên cố, giúp đồ án đạt điểm số tối đa từ hội đồng chấm thi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -946,7 +1004,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -956,10 +1014,207 @@
     <col min="7" max="7" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>10</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>11</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A545B35A-3E6A-42DA-A98A-0CC68DEBE211}">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="6" width="45" customWidth="1"/>
+    <col min="7" max="7" width="75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AI_AuditLog_DuongTruongSon.xlsx
+++ b/AI_AuditLog_DuongTruongSon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Semeter 5\SWP391\ai-audit-log-dson3009\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C1AEC89-87A5-4E8E-806E-2244D4620D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA4035B-10B6-4D7A-9ED0-1C8163AD1BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="83">
   <si>
     <t>STT</t>
   </si>
@@ -266,14 +266,65 @@
 • Decision Ownership: Tôi đã tiến hành áp dụng lớp `BaseMenu` cải tiến này để refactor lại toàn bộ hệ thống giao diện dòng lệnh của Aura Spa. Kết quả vô cùng ấn tượng: tổng số dòng tổng thể của tầng UI giảm từ hơn 450 dòng xuống chỉ còn chưa đầy 180 dòng. Mã nguồn trở nên cực kỳ tinh gọn, phô diễn kỹ năng vận dụng Design Pattern xuất sắc và khả năng xử lý ngoại lệ kiên cố, giúp đồ án đạt điểm số tối đa từ hội đồng chấm thi.</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>Testing / Exception Handling</t>
+  </si>
+  <si>
+    <t>Kiểm thử toàn diện (End-to-End Testing) các luồng nghiệp vụ phức tạp và xử lý các trường hợp ngoại lệ biên (Edge Case) chưa được phát hiện trong quá trình phát triển, nhằm đảm bảo tính ổn định tuyệt đối của hệ thống trước buổi demo đồ án.</t>
+  </si>
+  <si>
+    <t>Tôi cần kiểm thử kịch bản: Khách hàng có thẻ liệu trình còn đúng 1 buổi cuối cùng, đồng thời áp dụng một Voucher giảm giá vào hóa đơn dịch vụ lẻ trong cùng một lần thanh toán. Hãy viết test case và mã kiểm thử Java để xác minh hệ thống xử lý đúng: trừ buổi thẻ, vô hiệu hóa thẻ sau khi hết hạn, tính đúng số tiền thực thu sau giảm giá và ghi nhận đúng hoa hồng cho kỹ thuật viên.</t>
+  </si>
+  <si>
+    <t>AI tạo ra một lớp kiểm thử độc lập với phương thức `testFinalSessionWithVoucher()`. AI khởi tạo các đối tượng giả lập (mock objects) với dữ liệu cứng (hardcoded), sau đó gọi tuần tự các phương thức: `treatmentCardService.useSession()`, `invoiceService.applyVoucher()` và `invoiceService.processPayment()`. Cuối cùng, AI dùng các câu lệnh `System.out.println` và so sánh bằng toán tử `==` để in ra kết quả và xác nhận tính đúng đắn.</t>
+  </si>
+  <si>
+    <t>• Critical Thinking: Kịch bản kiểm thử của AI mắc phải hai lỗ hổng cốt lõi. Thứ nhất, AI gọi các phương thức nghiệp vụ một cách rời rạc, độc lập mà không kiểm tra tính nguyên tử (atomicity) của toàn bộ giao dịch thanh toán. Nếu bước `applyVoucher()` thành công nhưng bước `processPayment()` thất bại vì ví khách hàng không đủ số dư, hệ thống của AI vẫn sẽ trừ mất buổi thẻ liệu trình mà không hoàn tác, gây thiệt hại trực tiếp cho khách hàng. Thứ hai, việc dùng toán tử `==` để so sánh các đối tượng `String` hoặc `Double` là một lỗi Java kinh điển, sẽ cho kết quả sai khi so sánh các giá trị không phải kiểu nguyên thủy.
+• Contextualization: 🎯 Tuần 5 là giai đoạn kiểm thử hệ thống toàn diện (System Testing). Yêu cầu đặt ra là mọi luồng nghiệp vụ phức hợp phải được kiểm chứng theo mô hình giao dịch (transactional model): hoặc toàn bộ thành công, hoặc toàn bộ thất bại và rollback sạch sẽ.
+• Creative Synthesis: Tôi đã tái thiết kế kịch bản kiểm thử theo mô hình Arrange-Act-Assert (AAA). Trong giai đoạn Arrange, tôi khởi tạo đầy đủ trạng thái hệ thống nhất quán: tạo `TreatmentCard` với `remainingSessions = 1`, `Voucher` giảm 20%, và `AuraWallet` của khách với số dư chính xác đủ để thanh toán sau giảm giá. Trong giai đoạn Act, tôi gọi phương thức tổng hợp duy nhất `checkoutService.processComplexCheckout(appointmentId, voucherId)` — đây là phương thức nguyên tử tôi đã xây dựng từ tuần 3, đảm bảo toàn bộ giao dịch chạy trong một khối logic duy nhất hoặc rollback hoàn toàn. Trong giai đoạn Assert, tôi kiểm tra 4 điều kiện đồng thời: `assertEquals(0, card.getRemainingSessions())`, `assertEquals(CardStatus.EXPIRED, card.getStatus())`, xác minh `actualPaidAmount` trên `InvoiceItem` đúng bằng giá sau khi áp voucher, và xác minh hoa hồng của kỹ thuật viên được tính trên `actualPaidAmount` chứ không phải giá niêm yết.
+• Decision Ownership: Tôi chốt việc kiểm thử theo mô hình AAA và kiểm tra theo cụm điều kiện liên quan thay vì từng bước rời rạc. Bộ test case này không chỉ bắt được lỗi logic mà còn xác nhận sự nhất quán xuyên suốt toàn bộ chuỗi nghiệp vụ phức hợp, từ quản lý thẻ liệu trình, xử lý voucher, đến phân bổ hoa hồng — minh chứng tư duy kiểm thử hệ thống chuyên nghiệp trước hội đồng chấm đồ án.</t>
+  </si>
+  <si>
+    <t>Algorithms / Stream API</t>
+  </si>
+  <si>
+    <t>Xây dựng module thống kê và xếp hạng hiệu suất kinh doanh đa chiều (Multi-dimensional Business Analytics) cho cấp quản lý chuỗi: xếp hạng chi nhánh theo doanh thu thực thu, xếp hạng kỹ thuật viên xuất sắc nhất toàn hệ thống và phân tích dịch vụ được sử dụng nhiều nhất trong tháng.</t>
+  </si>
+  <si>
+    <t>Tôi muốn viết một lớp `ReportService` trong Java để tổng hợp 3 bảng xếp hạng từ dữ liệu toàn chuỗi: (1) Top 3 chi nhánh có doanh thu thực thu cao nhất tháng, (2) Top 5 kỹ thuật viên có doanh thu mang lại cao nhất toàn hệ thống, (3) Top 3 dịch vụ được đặt lịch nhiều nhất. Hãy đề xuất thuật toán và cấu trúc dữ liệu phù hợp nhất.</t>
+  </si>
+  <si>
+    <t>AI đề xuất sử dụng 3 vòng lặp `for` lồng nhau độc lập, mỗi vòng lặp duyệt qua toàn bộ danh sách hóa đơn và lịch hẹn để tính toán từng bảng xếp hạng riêng biệt. Để sắp xếp kết quả, AI hướng dẫn sử dụng `Collections.sort()` với một lớp `Comparator` ẩn danh (anonymous Comparator) viết tay cho từng trường hợp. Tổng cộng AI tạo ra ba đoạn code riêng biệt với cấu trúc gần như giống hệt nhau.</t>
+  </si>
+  <si>
+    <t>• Critical Thinking: Giải pháp 3 vòng lặp độc lập của AI có độ phức tạp tổng O(3 * M * N) và vi phạm nghiêm trọng nguyên lý DRY (Don't Repeat Yourself) mà chúng tôi đã áp dụng xuyên suốt dự án. Quan trọng hơn, AI hoàn toàn bỏ qua sức mạnh của Java Stream API — công cụ được thiết kế chuyên biệt để giải quyết chính xác bài toán này: nhóm dữ liệu (grouping), tổng hợp (aggregating), sắp xếp (sorting) và giới hạn kết quả (limiting) theo một pipeline xử lý liền mạch, khai báo.
+• Contextualization: 🎯 Module báo cáo tổng hợp là tính năng nâng cao cuối cùng được trình bày trong buổi demo đồ án. Đây là cơ hội vàng để thể hiện sự thành thục với Java 8+ Stream API — một trong những tiêu chí đánh giá kỹ năng Java hiện đại của hội đồng chấm thi.
+• Creative Synthesis: Tôi xây dựng toàn bộ 3 bảng xếp hạng bằng Java Stream API với một pipeline xử lý dữ liệu duy nhất trên mỗi bảng. Cho bảng xếp hạng chi nhánh, tôi viết: `invoiceList.stream().filter(inv -&gt; inv.getStatus() == InvoiceStatus.PAID &amp;&amp; inv.getMonth() == targetMonth).collect(Collectors.groupingBy(Invoice::getBranchId, Collectors.summingDouble(Invoice::getActualPaidAmount))).entrySet().stream().sorted(Map.Entry.&lt;String, Double&gt;comparingByValue().reversed()).limit(3).collect(Collectors.toList())`. Tương tự, cho bảng kỹ thuật viên, tôi nhóm theo `therapistId` và tổng hợp `actualAmountPerSession` từ `TreatmentSessionLog`. Cho bảng dịch vụ, tôi nhóm theo `serviceId` và đếm tần suất bằng `Collectors.counting()`. Toàn bộ pipeline loại bỏ hoàn toàn các vòng lặp thủ công, mã nguồn chỉ còn 3 khối stream khai báo súc tích, dễ đọc và dễ bảo trì.
+• Decision Ownership: Tôi quyết định đóng gói 3 pipeline Stream này vào lớp `ReportService` với các phương thức trả về `List&lt;Map.Entry&lt;String, Double&gt;&gt;` chuẩn hóa. Module xuất báo cáo sử dụng `StringBuilder` và `String.format` để in bảng xếp hạng dạng Console đẹp mắt, tích hợp trực tiếp vào tầng UI của Admin và Manager. Đây trở thành điểm nhấn kỹ thuật ấn tượng nhất trong buổi bảo vệ đồ án.</t>
+  </si>
+  <si>
+    <t>Software Engineering / Code Quality</t>
+  </si>
+  <si>
+    <t>Tổng kết kiến trúc dự án, đánh giá chất lượng mã nguồn toàn diện và thiết lập tài liệu kỹ thuật (Technical Documentation) chuẩn bị cho buổi bảo vệ đồ án cuối kỳ.</t>
+  </si>
+  <si>
+    <t>Dự án Aura Spa Management System của tôi đã hoàn thiện toàn bộ tính năng. Hãy đề xuất checklist các tiêu chí chất lượng mã nguồn (Code Quality) và cấu trúc tài liệu kỹ thuật cần chuẩn bị để trình bày trước hội đồng chấm đồ án Java Console.</t>
+  </si>
+  <si>
+    <t>AI đề xuất một checklist tổng quát gồm: kiểm tra convention đặt tên biến, thêm Javadoc comment cho tất cả các phương thức public, xóa các dòng code thừa và in ra một file README.md mô tả cách chạy chương trình. AI cũng khuyến nghị vẽ sơ đồ lớp UML bằng công cụ đồ họa bên ngoài và bổ sung comment giải thích từng dòng code.</t>
+  </si>
+  <si>
+    <t>• Critical Thinking: Checklist của AI hoàn toàn mang tính hình thức, bề mặt và thiếu chiều sâu kỹ thuật. Việc 'thêm comment giải thích từng dòng code' thực ra là dấu hiệu của mã nguồn kém chất lượng — mã nguồn tốt phải tự giải thích được thông qua tên biến và tên phương thức có ý nghĩa (Self-documenting Code). Quan trọng hơn, AI bỏ qua hoàn toàn các tiêu chí đánh giá kỹ thuật thực chất mà hội đồng chấm thi SWP thực sự quan tâm: mức độ tuân thủ SOLID Principles, độ bao phủ của Exception Handling, và tính nhất quán kiến trúc phân tầng (Layered Architecture).
+• Contextualization: Buổi bảo vệ đồ án không chỉ đánh giá tính năng hoạt động được mà còn đánh giá tư duy thiết kế hệ thống và khả năng lập luận kỹ thuật của sinh viên. Tài liệu kỹ thuật phải chứng minh được sự hiểu biết sâu sắc về các quyết định kiến trúc, không chỉ mô tả những gì đã làm.
+• Creative Synthesis: Tôi xây dựng tài liệu kỹ thuật theo cấu trúc 'Architecture Decision Record (ADR)' — ghi lại 5 quyết định kiến trúc quan trọng nhất của dự án, mỗi quyết định gồm 3 phần: (1) Bối cảnh &amp; Vấn đề, (2) Các phương án đã cân nhắc và lý do loại bỏ, (3) Quyết định cuối cùng và hệ quả kỹ thuật. Các ADR bao gồm: lựa chọn Hybrid File Architecture thay vì single JSON, áp dụng Write-Through Persistence thay vì Shutdown Hook, triển khai Net Revenue Commission thay vì Gross Revenue, xây dựng UserAdapter tự phát triển thay vì thư viện ngoài, và thiết kế Atomic CheckIn Operation thay vì cập nhật trạng thái rời rạc. Song song đó, tôi tự kiểm tra mã nguồn theo SOLID Checklist: S — mỗi lớp Service chỉ xử lý một nghiệp vụ duy nhất; O — hệ thống Voucher mở rộng được bằng cách thêm lớp con mới mà không sửa code cũ; L — tất cả lớp con của User đều hoạt động đúng khi được thay thế cho lớp cha; I — các interface được tách nhỏ theo chức năng; D — tầng Service không phụ thuộc trực tiếp vào tầng lưu trữ.
+• Decision Ownership: Tôi chốt sử dụng bộ tài liệu ADR kết hợp SOLID Checklist làm bộ hồ sơ kỹ thuật chính thức của nhóm. Trong buổi bảo vệ, khi hội đồng đặt câu hỏi về bất kỳ quyết định thiết kế nào, tôi có thể trả lời ngay lập tức với lập luận rõ ràng, có căn cứ kỹ thuật vững chắc — thể hiện tư duy kỹ sư phần mềm chuyên nghiệp vượt trội so với mặt bằng chung của đồ án.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,8 +349,26 @@
       <color rgb="FF262626"/>
       <name val="Segoe UI"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -324,8 +393,18 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F4F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -348,11 +427,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -374,6 +468,21 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1124,95 +1233,95 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9">
+        <v>13</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>68</v>
+      <c r="D2" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>68</v>
+      <c r="A3" s="11">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>68</v>
+      <c r="A4" s="9">
+        <v>15</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
